--- a/artfynd/A 60837-2023 artfynd.xlsx
+++ b/artfynd/A 60837-2023 artfynd.xlsx
@@ -1483,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119907086</v>
+        <v>119908100</v>
       </c>
       <c r="B9" t="n">
-        <v>91832</v>
+        <v>97907</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,52 +1495,51 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skog V travbanan, Skog V travbanan, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>794577</v>
+        <v>794557</v>
       </c>
       <c r="R9" t="n">
-        <v>7257250</v>
+        <v>7257236</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1564,7 +1563,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1578,7 +1577,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1597,7 +1595,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119908100</v>
+        <v>119907207</v>
       </c>
       <c r="B10" t="n">
         <v>97907</v>
@@ -1647,10 +1645,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>794557</v>
+        <v>794573</v>
       </c>
       <c r="R10" t="n">
-        <v>7257236</v>
+        <v>7257247</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1709,7 +1707,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119907207</v>
+        <v>119908385</v>
       </c>
       <c r="B11" t="n">
         <v>97907</v>
@@ -1759,10 +1757,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>794573</v>
+        <v>794475</v>
       </c>
       <c r="R11" t="n">
-        <v>7257247</v>
+        <v>7257222</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1821,10 +1819,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119908385</v>
+        <v>119907086</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>91832</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1833,51 +1831,52 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skog V travbanan, Skog V travbanan, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>794475</v>
+        <v>794577</v>
       </c>
       <c r="R12" t="n">
-        <v>7257222</v>
+        <v>7257250</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1901,20 +1900,21 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
           <t>2024-09-22</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2024-09-22</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 60837-2023 artfynd.xlsx
+++ b/artfynd/A 60837-2023 artfynd.xlsx
@@ -1258,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119884341</v>
+        <v>119899340</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,53 +1270,48 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skog V travbanan, Skog V travbanan, Nb</t>
+          <t>Skog V travbanan, Bergsviken, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>794532</v>
+        <v>794523</v>
       </c>
       <c r="R7" t="n">
-        <v>7257293</v>
+        <v>7257299</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1373,10 +1368,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119899340</v>
+        <v>119884341</v>
       </c>
       <c r="B8" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1385,48 +1380,53 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skog V travbanan, Bergsviken, Nb</t>
+          <t>Skog V travbanan, Skog V travbanan, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>794523</v>
+        <v>794532</v>
       </c>
       <c r="R8" t="n">
-        <v>7257299</v>
+        <v>7257293</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1483,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119908100</v>
+        <v>119907086</v>
       </c>
       <c r="B9" t="n">
-        <v>97907</v>
+        <v>91832</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,51 +1495,52 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skog V travbanan, Skog V travbanan, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>794557</v>
+        <v>794577</v>
       </c>
       <c r="R9" t="n">
-        <v>7257236</v>
+        <v>7257250</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1563,20 +1564,21 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
           <t>2024-09-22</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2024-09-22</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1595,7 +1597,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119907207</v>
+        <v>119908100</v>
       </c>
       <c r="B10" t="n">
         <v>97907</v>
@@ -1645,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>794573</v>
+        <v>794557</v>
       </c>
       <c r="R10" t="n">
-        <v>7257247</v>
+        <v>7257236</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1707,7 +1709,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119908385</v>
+        <v>119907207</v>
       </c>
       <c r="B11" t="n">
         <v>97907</v>
@@ -1757,10 +1759,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>794475</v>
+        <v>794573</v>
       </c>
       <c r="R11" t="n">
-        <v>7257222</v>
+        <v>7257247</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1819,10 +1821,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119907086</v>
+        <v>119908385</v>
       </c>
       <c r="B12" t="n">
-        <v>91832</v>
+        <v>97907</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,52 +1833,51 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skog V travbanan, Skog V travbanan, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>794577</v>
+        <v>794475</v>
       </c>
       <c r="R12" t="n">
-        <v>7257250</v>
+        <v>7257222</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1900,7 +1901,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1914,7 +1915,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 60837-2023 artfynd.xlsx
+++ b/artfynd/A 60837-2023 artfynd.xlsx
@@ -1258,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119899340</v>
+        <v>119884341</v>
       </c>
       <c r="B7" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,48 +1270,53 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skog V travbanan, Bergsviken, Nb</t>
+          <t>Skog V travbanan, Skog V travbanan, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>794523</v>
+        <v>794532</v>
       </c>
       <c r="R7" t="n">
-        <v>7257299</v>
+        <v>7257293</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1368,10 +1373,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119884341</v>
+        <v>119899340</v>
       </c>
       <c r="B8" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1380,53 +1385,48 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skog V travbanan, Skog V travbanan, Nb</t>
+          <t>Skog V travbanan, Bergsviken, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>794532</v>
+        <v>794523</v>
       </c>
       <c r="R8" t="n">
-        <v>7257293</v>
+        <v>7257299</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119908100</v>
+        <v>119907207</v>
       </c>
       <c r="B10" t="n">
         <v>97907</v>
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>794557</v>
+        <v>794573</v>
       </c>
       <c r="R10" t="n">
-        <v>7257236</v>
+        <v>7257247</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1709,7 +1709,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119907207</v>
+        <v>119908385</v>
       </c>
       <c r="B11" t="n">
         <v>97907</v>
@@ -1759,10 +1759,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>794573</v>
+        <v>794475</v>
       </c>
       <c r="R11" t="n">
-        <v>7257247</v>
+        <v>7257222</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1821,7 +1821,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119908385</v>
+        <v>119908100</v>
       </c>
       <c r="B12" t="n">
         <v>97907</v>
@@ -1871,10 +1871,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>794475</v>
+        <v>794557</v>
       </c>
       <c r="R12" t="n">
-        <v>7257222</v>
+        <v>7257236</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>

--- a/artfynd/A 60837-2023 artfynd.xlsx
+++ b/artfynd/A 60837-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1931,6 +1931,118 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120337605</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Skog V travbanan, Skog V travbanan, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>794421</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7257239</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60837-2023 artfynd.xlsx
+++ b/artfynd/A 60837-2023 artfynd.xlsx
@@ -1258,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119884341</v>
+        <v>119899340</v>
       </c>
       <c r="B7" t="n">
-        <v>97907</v>
+        <v>91858</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,53 +1270,48 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skog V travbanan, Skog V travbanan, Nb</t>
+          <t>Skog V travbanan, Bergsviken, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>794532</v>
+        <v>794523</v>
       </c>
       <c r="R7" t="n">
-        <v>7257293</v>
+        <v>7257299</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1373,10 +1368,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119899340</v>
+        <v>119884341</v>
       </c>
       <c r="B8" t="n">
-        <v>91840</v>
+        <v>97930</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1385,48 +1380,53 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skog V travbanan, Bergsviken, Nb</t>
+          <t>Skog V travbanan, Skog V travbanan, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>794523</v>
+        <v>794532</v>
       </c>
       <c r="R8" t="n">
-        <v>7257299</v>
+        <v>7257293</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>119907086</v>
       </c>
       <c r="B9" t="n">
-        <v>91832</v>
+        <v>91850</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1597,10 +1597,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119907207</v>
+        <v>119908100</v>
       </c>
       <c r="B10" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>794573</v>
+        <v>794557</v>
       </c>
       <c r="R10" t="n">
-        <v>7257247</v>
+        <v>7257236</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119908385</v>
+        <v>119907207</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1759,10 +1759,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>794475</v>
+        <v>794573</v>
       </c>
       <c r="R11" t="n">
-        <v>7257222</v>
+        <v>7257247</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1821,10 +1821,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119908100</v>
+        <v>119908385</v>
       </c>
       <c r="B12" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1871,10 +1871,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>794557</v>
+        <v>794475</v>
       </c>
       <c r="R12" t="n">
-        <v>7257236</v>
+        <v>7257222</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>

--- a/artfynd/A 60837-2023 artfynd.xlsx
+++ b/artfynd/A 60837-2023 artfynd.xlsx
@@ -1483,10 +1483,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119907086</v>
+        <v>119907207</v>
       </c>
       <c r="B9" t="n">
-        <v>91850</v>
+        <v>97930</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,52 +1495,51 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skog V travbanan, Skog V travbanan, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>794577</v>
+        <v>794573</v>
       </c>
       <c r="R9" t="n">
-        <v>7257250</v>
+        <v>7257247</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1564,7 +1563,7 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1578,7 +1577,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1597,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119908100</v>
+        <v>119907086</v>
       </c>
       <c r="B10" t="n">
-        <v>97930</v>
+        <v>91850</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1609,51 +1607,52 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skog V travbanan, Skog V travbanan, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>794557</v>
+        <v>794577</v>
       </c>
       <c r="R10" t="n">
-        <v>7257236</v>
+        <v>7257250</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1677,20 +1676,21 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
           <t>2024-09-22</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2024-09-22</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1709,7 +1709,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119907207</v>
+        <v>119908100</v>
       </c>
       <c r="B11" t="n">
         <v>97930</v>
@@ -1759,10 +1759,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>794573</v>
+        <v>794557</v>
       </c>
       <c r="R11" t="n">
-        <v>7257247</v>
+        <v>7257236</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 60837-2023 artfynd.xlsx
+++ b/artfynd/A 60837-2023 artfynd.xlsx
@@ -1483,7 +1483,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119907207</v>
+        <v>119908100</v>
       </c>
       <c r="B9" t="n">
         <v>97930</v>
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>794573</v>
+        <v>794557</v>
       </c>
       <c r="R9" t="n">
-        <v>7257247</v>
+        <v>7257236</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1709,7 +1709,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119908100</v>
+        <v>119908385</v>
       </c>
       <c r="B11" t="n">
         <v>97930</v>
@@ -1759,10 +1759,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>794557</v>
+        <v>794475</v>
       </c>
       <c r="R11" t="n">
-        <v>7257236</v>
+        <v>7257222</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1821,7 +1821,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119908385</v>
+        <v>119907207</v>
       </c>
       <c r="B12" t="n">
         <v>97930</v>
@@ -1871,10 +1871,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>794475</v>
+        <v>794573</v>
       </c>
       <c r="R12" t="n">
-        <v>7257222</v>
+        <v>7257247</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>

--- a/artfynd/A 60837-2023 artfynd.xlsx
+++ b/artfynd/A 60837-2023 artfynd.xlsx
@@ -1709,7 +1709,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119908385</v>
+        <v>119907207</v>
       </c>
       <c r="B11" t="n">
         <v>97930</v>
@@ -1759,10 +1759,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>794475</v>
+        <v>794573</v>
       </c>
       <c r="R11" t="n">
-        <v>7257222</v>
+        <v>7257247</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1821,7 +1821,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119907207</v>
+        <v>119908385</v>
       </c>
       <c r="B12" t="n">
         <v>97930</v>
@@ -1871,10 +1871,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>794573</v>
+        <v>794475</v>
       </c>
       <c r="R12" t="n">
-        <v>7257247</v>
+        <v>7257222</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>

--- a/artfynd/A 60837-2023 artfynd.xlsx
+++ b/artfynd/A 60837-2023 artfynd.xlsx
@@ -1258,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119899340</v>
+        <v>119884341</v>
       </c>
       <c r="B7" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,48 +1270,53 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skog V travbanan, Bergsviken, Nb</t>
+          <t>Skog V travbanan, Skog V travbanan, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>794523</v>
+        <v>794532</v>
       </c>
       <c r="R7" t="n">
-        <v>7257299</v>
+        <v>7257293</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1368,10 +1373,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119884341</v>
+        <v>119899340</v>
       </c>
       <c r="B8" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1380,53 +1385,48 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skog V travbanan, Skog V travbanan, Nb</t>
+          <t>Skog V travbanan, Bergsviken, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>794532</v>
+        <v>794523</v>
       </c>
       <c r="R8" t="n">
-        <v>7257293</v>
+        <v>7257299</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1595,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119907086</v>
+        <v>119907207</v>
       </c>
       <c r="B10" t="n">
-        <v>91850</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,52 +1607,51 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skog V travbanan, Skog V travbanan, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>794577</v>
+        <v>794573</v>
       </c>
       <c r="R10" t="n">
-        <v>7257250</v>
+        <v>7257247</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1676,7 +1675,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1690,7 +1689,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1709,7 +1707,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119907207</v>
+        <v>119908385</v>
       </c>
       <c r="B11" t="n">
         <v>97930</v>
@@ -1759,10 +1757,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>794573</v>
+        <v>794475</v>
       </c>
       <c r="R11" t="n">
-        <v>7257247</v>
+        <v>7257222</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1821,10 +1819,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119908385</v>
+        <v>119907086</v>
       </c>
       <c r="B12" t="n">
-        <v>97930</v>
+        <v>91850</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1833,51 +1831,52 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skog V travbanan, Skog V travbanan, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>794475</v>
+        <v>794577</v>
       </c>
       <c r="R12" t="n">
-        <v>7257222</v>
+        <v>7257250</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1901,20 +1900,21 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
           <t>2024-09-22</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2024-09-22</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 60837-2023 artfynd.xlsx
+++ b/artfynd/A 60837-2023 artfynd.xlsx
@@ -1483,7 +1483,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119908100</v>
+        <v>119908385</v>
       </c>
       <c r="B9" t="n">
         <v>97930</v>
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>794557</v>
+        <v>794475</v>
       </c>
       <c r="R9" t="n">
-        <v>7257236</v>
+        <v>7257222</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1595,10 +1595,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119907207</v>
+        <v>119907086</v>
       </c>
       <c r="B10" t="n">
-        <v>97930</v>
+        <v>91850</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,51 +1607,52 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skog V travbanan, Skog V travbanan, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>794573</v>
+        <v>794577</v>
       </c>
       <c r="R10" t="n">
-        <v>7257247</v>
+        <v>7257250</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1675,20 +1676,21 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
+          <t>2024-09-21</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
           <t>2024-09-22</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2024-09-22</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1707,7 +1709,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119908385</v>
+        <v>119907207</v>
       </c>
       <c r="B11" t="n">
         <v>97930</v>
@@ -1757,10 +1759,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>794475</v>
+        <v>794573</v>
       </c>
       <c r="R11" t="n">
-        <v>7257222</v>
+        <v>7257247</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1819,10 +1821,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119907086</v>
+        <v>119908100</v>
       </c>
       <c r="B12" t="n">
-        <v>91850</v>
+        <v>97930</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,52 +1833,51 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skog V travbanan, Skog V travbanan, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>794577</v>
+        <v>794557</v>
       </c>
       <c r="R12" t="n">
-        <v>7257250</v>
+        <v>7257236</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1900,7 +1901,7 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1914,7 +1915,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 60837-2023 artfynd.xlsx
+++ b/artfynd/A 60837-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2043,6 +2043,220 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>124914372</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Fagerberget sluttning, Fagerberget sluttning, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>794439</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7257189</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>124916984</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Fagerberget sluttning, Bergsviken, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>794563</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7257209</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60837-2023 artfynd.xlsx
+++ b/artfynd/A 60837-2023 artfynd.xlsx
@@ -2045,7 +2045,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124914372</v>
+        <v>124916984</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2079,16 +2079,26 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fagerberget sluttning, Fagerberget sluttning, Nb</t>
+          <t>Fagerberget sluttning, Bergsviken, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>794439</v>
+        <v>794563</v>
       </c>
       <c r="R14" t="n">
-        <v>7257189</v>
+        <v>7257209</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2147,7 +2157,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124916984</v>
+        <v>124914372</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2181,26 +2191,16 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fagerberget sluttning, Bergsviken, Nb</t>
+          <t>Fagerberget sluttning, Fagerberget sluttning, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>794563</v>
+        <v>794439</v>
       </c>
       <c r="R15" t="n">
-        <v>7257209</v>
+        <v>7257189</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>

--- a/artfynd/A 60837-2023 artfynd.xlsx
+++ b/artfynd/A 60837-2023 artfynd.xlsx
@@ -2045,7 +2045,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124916984</v>
+        <v>124914372</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2079,26 +2079,16 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fagerberget sluttning, Bergsviken, Nb</t>
+          <t>Fagerberget sluttning, Fagerberget sluttning, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>794563</v>
+        <v>794439</v>
       </c>
       <c r="R14" t="n">
-        <v>7257209</v>
+        <v>7257189</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2157,7 +2147,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124914372</v>
+        <v>124916984</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2191,16 +2181,26 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fagerberget sluttning, Fagerberget sluttning, Nb</t>
+          <t>Fagerberget sluttning, Bergsviken, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>794439</v>
+        <v>794563</v>
       </c>
       <c r="R15" t="n">
-        <v>7257189</v>
+        <v>7257209</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>

--- a/artfynd/A 60837-2023 artfynd.xlsx
+++ b/artfynd/A 60837-2023 artfynd.xlsx
@@ -2048,7 +2048,7 @@
         <v>124914372</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
         <v>124916984</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>

--- a/artfynd/A 60837-2023 artfynd.xlsx
+++ b/artfynd/A 60837-2023 artfynd.xlsx
@@ -2045,7 +2045,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124914372</v>
+        <v>124916984</v>
       </c>
       <c r="B14" t="n">
         <v>98269</v>
@@ -2079,16 +2079,26 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fagerberget sluttning, Fagerberget sluttning, Nb</t>
+          <t>Fagerberget sluttning, Bergsviken, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>794439</v>
+        <v>794563</v>
       </c>
       <c r="R14" t="n">
-        <v>7257189</v>
+        <v>7257209</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2147,7 +2157,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124916984</v>
+        <v>124914372</v>
       </c>
       <c r="B15" t="n">
         <v>98269</v>
@@ -2181,26 +2191,16 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fagerberget sluttning, Bergsviken, Nb</t>
+          <t>Fagerberget sluttning, Fagerberget sluttning, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>794563</v>
+        <v>794439</v>
       </c>
       <c r="R15" t="n">
-        <v>7257209</v>
+        <v>7257189</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>

--- a/artfynd/A 60837-2023 artfynd.xlsx
+++ b/artfynd/A 60837-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2050,11 +2050,6 @@
       <c r="B14" t="n">
         <v>98269</v>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D14" t="inlineStr">
         <is>
           <t>VU</t>
@@ -2162,11 +2157,6 @@
       <c r="B15" t="n">
         <v>98269</v>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D15" t="inlineStr">
         <is>
           <t>VU</t>
@@ -2256,6 +2246,225 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>125731813</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98324</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Fagerberget sluttning, Fagerberget sluttning, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>794397</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7257260</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>125732173</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98324</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Fagerberget sluttning, Fagerberget sluttning, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>794392</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7257175</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Åtskilliga plantor högt upp i sluttningen i granskog.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60837-2023 artfynd.xlsx
+++ b/artfynd/A 60837-2023 artfynd.xlsx
@@ -2252,7 +2252,7 @@
         <v>125731813</v>
       </c>
       <c r="B16" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>125732173</v>
       </c>
       <c r="B17" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 60837-2023 artfynd.xlsx
+++ b/artfynd/A 60837-2023 artfynd.xlsx
@@ -2252,7 +2252,7 @@
         <v>125731813</v>
       </c>
       <c r="B16" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>125732173</v>
       </c>
       <c r="B17" t="n">
-        <v>98331</v>
+        <v>98332</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 60837-2023 artfynd.xlsx
+++ b/artfynd/A 60837-2023 artfynd.xlsx
@@ -2252,7 +2252,7 @@
         <v>125731813</v>
       </c>
       <c r="B16" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>125732173</v>
       </c>
       <c r="B17" t="n">
-        <v>98332</v>
+        <v>98334</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 60837-2023 artfynd.xlsx
+++ b/artfynd/A 60837-2023 artfynd.xlsx
@@ -2252,7 +2252,7 @@
         <v>125731813</v>
       </c>
       <c r="B16" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>125732173</v>
       </c>
       <c r="B17" t="n">
-        <v>98334</v>
+        <v>98338</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 60837-2023 artfynd.xlsx
+++ b/artfynd/A 60837-2023 artfynd.xlsx
@@ -2252,7 +2252,7 @@
         <v>125731813</v>
       </c>
       <c r="B16" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>125732173</v>
       </c>
       <c r="B17" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 60837-2023 artfynd.xlsx
+++ b/artfynd/A 60837-2023 artfynd.xlsx
@@ -2252,7 +2252,7 @@
         <v>125731813</v>
       </c>
       <c r="B16" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>125732173</v>
       </c>
       <c r="B17" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 60837-2023 artfynd.xlsx
+++ b/artfynd/A 60837-2023 artfynd.xlsx
@@ -2252,7 +2252,7 @@
         <v>125731813</v>
       </c>
       <c r="B16" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>125732173</v>
       </c>
       <c r="B17" t="n">
-        <v>98341</v>
+        <v>98343</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 60837-2023 artfynd.xlsx
+++ b/artfynd/A 60837-2023 artfynd.xlsx
@@ -2252,7 +2252,7 @@
         <v>125731813</v>
       </c>
       <c r="B16" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>125732173</v>
       </c>
       <c r="B17" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 60837-2023 artfynd.xlsx
+++ b/artfynd/A 60837-2023 artfynd.xlsx
@@ -2252,7 +2252,7 @@
         <v>125731813</v>
       </c>
       <c r="B16" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>125732173</v>
       </c>
       <c r="B17" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 60837-2023 artfynd.xlsx
+++ b/artfynd/A 60837-2023 artfynd.xlsx
@@ -2252,7 +2252,7 @@
         <v>125731813</v>
       </c>
       <c r="B16" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>125732173</v>
       </c>
       <c r="B17" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 60837-2023 artfynd.xlsx
+++ b/artfynd/A 60837-2023 artfynd.xlsx
@@ -2252,7 +2252,7 @@
         <v>125731813</v>
       </c>
       <c r="B16" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2359,7 +2359,7 @@
         <v>125732173</v>
       </c>
       <c r="B17" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/A 60837-2023 artfynd.xlsx
+++ b/artfynd/A 60837-2023 artfynd.xlsx
@@ -2587,7 +2587,7 @@
         <v>133290444</v>
       </c>
       <c r="B19" t="n">
-        <v>97995</v>
+        <v>97997</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>133290344</v>
       </c>
       <c r="B20" t="n">
-        <v>97995</v>
+        <v>97997</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 60837-2023 artfynd.xlsx
+++ b/artfynd/A 60837-2023 artfynd.xlsx
@@ -2587,7 +2587,7 @@
         <v>133290444</v>
       </c>
       <c r="B19" t="n">
-        <v>97997</v>
+        <v>98005</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>133290344</v>
       </c>
       <c r="B20" t="n">
-        <v>97997</v>
+        <v>98005</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 60837-2023 artfynd.xlsx
+++ b/artfynd/A 60837-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,67 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119199976</v>
+        <v>119907086</v>
       </c>
       <c r="B2" t="n">
-        <v>97905</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skog V travbanan (Skog V travbanan), Nb</t>
+          <t>Skog V travbanan, Skog V travbanan, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>794390</v>
+        <v>794577</v>
       </c>
       <c r="R2" t="n">
-        <v>7257132</v>
+        <v>7257250</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,12 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,6 +765,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -791,67 +784,55 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119200511</v>
+        <v>119899340</v>
       </c>
       <c r="B3" t="n">
-        <v>97905</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skog V travbanan (Skog V travbanan), Nb</t>
+          <t>Skog V travbanan, Bergsviken, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>794574</v>
+        <v>794523</v>
       </c>
       <c r="R3" t="n">
-        <v>7257252</v>
+        <v>7257299</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,12 +856,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,6 +870,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -907,67 +889,53 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119198222</v>
+        <v>133289720</v>
       </c>
       <c r="B4" t="n">
-        <v>97905</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skog V travbanan (Skog V travbanan), Nb</t>
+          <t>Sumpskog V travbanan, Bergsviken, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>794451</v>
+        <v>794719</v>
       </c>
       <c r="R4" t="n">
-        <v>7257174</v>
+        <v>7257355</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,12 +959,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Decimeterstort hål i björk, färska spånor under.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,67 +996,57 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119200419</v>
+        <v>131671296</v>
       </c>
       <c r="B5" t="n">
-        <v>97905</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57816</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>102621</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skog V travbanan (Skog V travbanan), Nb</t>
+          <t>Sumpskog V travbanan, Bergsviken, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>794580</v>
+        <v>794707</v>
       </c>
       <c r="R5" t="n">
-        <v>7257214</v>
+        <v>7257303</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1107,12 +1070,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,69 +1112,56 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119200052</v>
+        <v>133289732</v>
       </c>
       <c r="B6" t="n">
-        <v>97905</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57816</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>102621</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skog V travbanan (Skog V travbanan), Nb</t>
+          <t>Sumpskog V travbanan, Bergsviken, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>794432</v>
+        <v>794730</v>
       </c>
       <c r="R6" t="n">
-        <v>7257200</v>
+        <v>7257351</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1225,12 +1185,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Två spybollar och även fragment av en spyboll med rester av en fågelfjäder i. Storlek ca 12x30 mm, vilket stämmer med litteraturuppgift.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1239,7 +1204,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1258,15 +1222,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119884341</v>
+        <v>119197647</v>
       </c>
       <c r="B7" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1291,15 +1250,19 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -1310,10 +1273,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>794532</v>
+        <v>794451</v>
       </c>
       <c r="R7" t="n">
-        <v>7257293</v>
+        <v>7257174</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1340,12 +1303,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1373,60 +1336,62 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119899340</v>
+        <v>119199976</v>
       </c>
       <c r="B8" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skog V travbanan, Bergsviken, Nb</t>
+          <t>Skog V travbanan, Skog V travbanan, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>794523</v>
+        <v>794390</v>
       </c>
       <c r="R8" t="n">
-        <v>7257299</v>
+        <v>7257132</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1450,12 +1415,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,7 +1429,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1483,15 +1447,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119908385</v>
+        <v>119200052</v>
       </c>
       <c r="B9" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1516,10 +1475,14 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1527,16 +1490,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Skog V travbanan, Skog V travbanan, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>794475</v>
+        <v>794432</v>
       </c>
       <c r="R9" t="n">
-        <v>7257222</v>
+        <v>7257200</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1563,12 +1528,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1577,6 +1542,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1595,64 +1561,62 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119907086</v>
+        <v>119200419</v>
       </c>
       <c r="B10" t="n">
-        <v>91850</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4361</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skog V travbanan, Skog V travbanan, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>794577</v>
+        <v>794580</v>
       </c>
       <c r="R10" t="n">
-        <v>7257250</v>
+        <v>7257214</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1676,12 +1640,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-21</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1690,7 +1654,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1709,15 +1672,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119907207</v>
+        <v>119200511</v>
       </c>
       <c r="B11" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1742,10 +1700,14 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1759,13 +1721,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>794573</v>
+        <v>794574</v>
       </c>
       <c r="R11" t="n">
-        <v>7257247</v>
+        <v>7257252</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1789,12 +1751,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1821,15 +1783,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119908100</v>
+        <v>119884341</v>
       </c>
       <c r="B12" t="n">
-        <v>97930</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1865,16 +1822,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skog V travbanan, Skog V travbanan, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>794557</v>
+        <v>794532</v>
       </c>
       <c r="R12" t="n">
-        <v>7257236</v>
+        <v>7257293</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1901,12 +1860,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-22</t>
+          <t>2024-09-21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1915,6 +1874,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1933,15 +1893,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120337605</v>
+        <v>119907207</v>
       </c>
       <c r="B13" t="n">
-        <v>98007</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1983,10 +1938,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>794421</v>
+        <v>794573</v>
       </c>
       <c r="R13" t="n">
-        <v>7257239</v>
+        <v>7257247</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2013,12 +1968,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2045,10 +2000,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124916984</v>
+        <v>119908100</v>
       </c>
       <c r="B14" t="n">
-        <v>98269</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2086,14 +2041,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Fagerberget sluttning, Bergsviken, Nb</t>
+          <t>Skog V travbanan, Skog V travbanan, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>794563</v>
+        <v>794557</v>
       </c>
       <c r="R14" t="n">
-        <v>7257209</v>
+        <v>7257236</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2120,12 +2075,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2152,10 +2107,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124914372</v>
+        <v>119908385</v>
       </c>
       <c r="B15" t="n">
-        <v>98269</v>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2181,16 +2136,26 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Fagerberget sluttning, Fagerberget sluttning, Nb</t>
+          <t>Skog V travbanan, Skog V travbanan, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>794439</v>
+        <v>794475</v>
       </c>
       <c r="R15" t="n">
-        <v>7257189</v>
+        <v>7257222</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2217,12 +2182,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-05-10</t>
+          <t>2024-09-22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2249,10 +2214,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125731813</v>
+        <v>120337605</v>
       </c>
       <c r="B16" t="n">
-        <v>98361</v>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2290,17 +2255,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Fagerberget sluttning, Fagerberget sluttning, Nb</t>
+          <t>Skog V travbanan, Skog V travbanan, Nb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>794397</v>
+        <v>794421</v>
       </c>
       <c r="R16" t="n">
-        <v>7257260</v>
+        <v>7257239</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2324,12 +2289,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2024-10-11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2356,10 +2321,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125732173</v>
+        <v>124914372</v>
       </c>
       <c r="B17" t="n">
-        <v>98361</v>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2385,29 +2350,19 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Fagerberget sluttning, Fagerberget sluttning, Nb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>794392</v>
+        <v>794439</v>
       </c>
       <c r="R17" t="n">
-        <v>7257175</v>
+        <v>7257189</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2431,17 +2386,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Åtskilliga plantor högt upp i sluttningen i granskog.</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2468,57 +2418,58 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131671296</v>
+        <v>124916984</v>
       </c>
       <c r="B18" t="n">
-        <v>57789</v>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102621</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sumpskog V travbanan, Bergsviken, Nb</t>
+          <t>Fagerberget sluttning, Bergsviken, Nb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>794707</v>
+        <v>794563</v>
       </c>
       <c r="R18" t="n">
-        <v>7257303</v>
+        <v>7257209</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2542,22 +2493,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>18:15</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-03-15</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>18:15</t>
+          <t>2025-05-10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2584,57 +2525,58 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133290444</v>
+        <v>125731813</v>
       </c>
       <c r="B19" t="n">
-        <v>98043</v>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sumpskog V travbanan, Sumpskog V travbanan, Nb</t>
+          <t>Fagerberget sluttning, Fagerberget sluttning, Nb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>794688</v>
+        <v>794397</v>
       </c>
       <c r="R19" t="n">
-        <v>7257283</v>
+        <v>7257260</v>
       </c>
       <c r="S19" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2658,12 +2600,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2690,57 +2632,58 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133290344</v>
+        <v>125732173</v>
       </c>
       <c r="B20" t="n">
-        <v>98043</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sumpskog V travbanan, Sumpskog V travbanan, Nb</t>
+          <t>Fagerberget sluttning, Fagerberget sluttning, Nb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>794699</v>
+        <v>794392</v>
       </c>
       <c r="R20" t="n">
-        <v>7257279</v>
+        <v>7257175</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2764,12 +2707,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2025-06-06</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Åtskilliga plantor högt upp i sluttningen i granskog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2793,6 +2741,218 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>133290344</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Sumpskog V travbanan, Sumpskog V travbanan, Nb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>794699</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7257279</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>133290444</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Sumpskog V travbanan, Sumpskog V travbanan, Nb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>794688</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7257283</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60837-2023 artfynd.xlsx
+++ b/artfynd/A 60837-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2744,37 +2744,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133290344</v>
+        <v>134491656</v>
       </c>
       <c r="B21" t="n">
-        <v>98060</v>
+        <v>99195</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2782,19 +2782,24 @@
           <t>m²</t>
         </is>
       </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sumpskog V travbanan, Sumpskog V travbanan, Nb</t>
+          <t>Skog V travbanan, Skog V travbanan, Nb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>794699</v>
+        <v>794550</v>
       </c>
       <c r="R21" t="n">
-        <v>7257279</v>
+        <v>7257219</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2818,12 +2823,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2850,7 +2855,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133290444</v>
+        <v>133290344</v>
       </c>
       <c r="B22" t="n">
         <v>98060</v>
@@ -2880,7 +2885,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2894,13 +2899,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>794688</v>
+        <v>794699</v>
       </c>
       <c r="R22" t="n">
-        <v>7257283</v>
+        <v>7257279</v>
       </c>
       <c r="S22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2953,6 +2958,112 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>133290444</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Sumpskog V travbanan, Sumpskog V travbanan, Nb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>794688</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7257283</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hortlax</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Tomas Carlsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60837-2023 artfynd.xlsx
+++ b/artfynd/A 60837-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119907086</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119899340</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133289720</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1109,6 +1129,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131671296</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1219,6 +1244,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133289732</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1333,6 +1363,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119197647</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1444,6 +1479,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119199976</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1558,6 +1598,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119200052</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1669,6 +1714,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119200419</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1780,6 +1830,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119200511</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1890,6 +1945,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119884341</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1997,6 +2057,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119907207</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2104,6 +2169,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119908100</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2211,6 +2281,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119908385</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2318,6 +2393,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120337605</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2415,6 +2495,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124914372</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2522,6 +2607,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124916984</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2629,6 +2719,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125731813</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2741,6 +2836,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125732173</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2852,6 +2952,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134491656</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2958,6 +3063,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133290344</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3064,8 +3174,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133290444</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>